--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.91510407894719</v>
+        <v>3.236204412828918</v>
       </c>
       <c r="D2" t="n">
-        <v>18.56966619705344</v>
+        <v>3.017570757021184</v>
       </c>
       <c r="E2" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F2" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.986985690753444</v>
+        <v>0.8103851747474348</v>
       </c>
       <c r="D3" t="n">
-        <v>3.639724853558572</v>
+        <v>0.591455288703268</v>
       </c>
       <c r="E3" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F3" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.68874970035748</v>
+        <v>2.386921826308091</v>
       </c>
       <c r="D4" t="n">
-        <v>13.94390557447911</v>
+        <v>2.265884655852855</v>
       </c>
       <c r="E4" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F4" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.8815007475558</v>
+        <v>9.243243871477818</v>
       </c>
       <c r="D5" t="n">
-        <v>56.25296162854642</v>
+        <v>9.141106264638793</v>
       </c>
       <c r="E5" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F5" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.09403694132048</v>
+        <v>6.352781002964578</v>
       </c>
       <c r="D6" t="n">
-        <v>39.66765420229299</v>
+        <v>6.445993807872612</v>
       </c>
       <c r="E6" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F6" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.55240182351741</v>
+        <v>4.15226529632158</v>
       </c>
       <c r="D7" t="n">
-        <v>26.5297357432954</v>
+        <v>4.311082058285503</v>
       </c>
       <c r="E7" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F7" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.56007262643984</v>
+        <v>6.266011801796474</v>
       </c>
       <c r="D8" t="n">
-        <v>38.86575430768265</v>
+        <v>6.315685074998431</v>
       </c>
       <c r="E8" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F8" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.74215680491746</v>
+        <v>5.483100480799088</v>
       </c>
       <c r="D9" t="n">
-        <v>34.01442352728692</v>
+        <v>5.527343823184125</v>
       </c>
       <c r="E9" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F9" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.75082487346378</v>
+        <v>3.372009041937864</v>
       </c>
       <c r="D10" t="n">
-        <v>20.23458552211967</v>
+        <v>3.288120147344446</v>
       </c>
       <c r="E10" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F10" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.24381562817142</v>
+        <v>4.589620039577856</v>
       </c>
       <c r="D11" t="n">
-        <v>28.11190247243805</v>
+        <v>4.568184151771184</v>
       </c>
       <c r="E11" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F11" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.46265719788875</v>
+        <v>3.162681794656921</v>
       </c>
       <c r="D12" t="n">
-        <v>19.73179960060887</v>
+        <v>3.206417435098941</v>
       </c>
       <c r="E12" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F12" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.19921757058058</v>
+        <v>4.419872855219344</v>
       </c>
       <c r="D13" t="n">
-        <v>26.73415617000679</v>
+        <v>4.344300377626103</v>
       </c>
       <c r="E13" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F13" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.00918712138424</v>
+        <v>6.501492907224939</v>
       </c>
       <c r="D14" t="n">
-        <v>39.08531245513582</v>
+        <v>6.351363273959571</v>
       </c>
       <c r="E14" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F14" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.5290212614304</v>
+        <v>7.23596595498244</v>
       </c>
       <c r="D15" t="n">
-        <v>43.76829601802626</v>
+        <v>7.112348102929268</v>
       </c>
       <c r="E15" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F15" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>53.17911950668843</v>
+        <v>8.641606919836871</v>
       </c>
       <c r="D16" t="n">
-        <v>52.34948191304959</v>
+        <v>8.506790810870559</v>
       </c>
       <c r="E16" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F16" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>46.72923349682254</v>
+        <v>7.593500443233663</v>
       </c>
       <c r="D17" t="n">
-        <v>47.35510152965174</v>
+        <v>7.695203998568408</v>
       </c>
       <c r="E17" t="n">
-        <v>14.00859490494773</v>
+        <v>2.276396672054006</v>
       </c>
       <c r="F17" t="n">
-        <v>14.16103301127441</v>
+        <v>2.301167864332091</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
